--- a/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
+++ b/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6984C88F-F72A-45E1-B416-A20AE792BBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26CAA05-136F-43AD-90F3-9ADBFE364E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="6" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="236">
   <si>
     <t>Scenario</t>
   </si>
@@ -4108,231 +4108,7 @@
 - Docks unlocked</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Victory</t>
-  </si>
-  <si>
-    <t>UniteTheHuns</t>
-  </si>
-  <si>
-    <t>FreeVillagers</t>
-  </si>
-  <si>
-    <t>ResolveScoutAny</t>
-  </si>
-  <si>
-    <t>CaptureHorsesCamp</t>
-  </si>
-  <si>
-    <t>CaptureHorseRuins</t>
-  </si>
-  <si>
-    <t>CaptureHorsesLumber</t>
-  </si>
-  <si>
-    <t>CaptureHorsesBehindBase</t>
-  </si>
-  <si>
-    <t>CaptureHorsesWest</t>
-  </si>
-  <si>
-    <t>CaptureHorsesRoman</t>
-  </si>
-  <si>
-    <t>KillTheBoar</t>
-  </si>
-  <si>
-    <t>BetrayBleda</t>
-  </si>
-  <si>
-    <t>BlowBledaOff</t>
-  </si>
-  <si>
-    <t>FreeScout</t>
-  </si>
-  <si>
-    <t>KillScout</t>
-  </si>
-  <si>
-    <t>GiveHorses</t>
-  </si>
-  <si>
-    <t>DefeatFirstPlayer</t>
-  </si>
-  <si>
-    <t>DefeatsanityBlue</t>
-  </si>
-  <si>
-    <t>DefeatsanityRed</t>
-  </si>
-  <si>
-    <t>DefeatsanityGreen</t>
-  </si>
-  <si>
     <t>No items required</t>
-  </si>
-  <si>
-    <t>Requires 'UniteTheHuns'
-Otherwise the flagged Area is closed off</t>
-  </si>
-  <si>
-    <t>RedTC</t>
-  </si>
-  <si>
-    <t>GreenLumber</t>
-  </si>
-  <si>
-    <t>PurpleVills</t>
-  </si>
-  <si>
-    <t>GreyMining</t>
-  </si>
-  <si>
-    <t>CyanTC</t>
-  </si>
-  <si>
-    <t>ScythianVills</t>
-  </si>
-  <si>
-    <t>BuildTC</t>
-  </si>
-  <si>
-    <t>BeatTheRomans</t>
-  </si>
-  <si>
-    <t>DefeatsanityCyan</t>
-  </si>
-  <si>
-    <t>DefeatsanityGrey</t>
-  </si>
-  <si>
-    <t>DefeatsanityPurple</t>
-  </si>
-  <si>
-    <t>DefeatsanityOrange</t>
-  </si>
-  <si>
-    <t>GreenDock1</t>
-  </si>
-  <si>
-    <t>GreenDock2</t>
-  </si>
-  <si>
-    <t>FindGold</t>
-  </si>
-  <si>
-    <t>GreenTC</t>
-  </si>
-  <si>
-    <t>BlueDockNorth</t>
-  </si>
-  <si>
-    <t>BlueDocksSouth</t>
-  </si>
-  <si>
-    <t>BuildCastle</t>
-  </si>
-  <si>
-    <t>RedTradeCarts</t>
-  </si>
-  <si>
-    <t>BlueCogs</t>
-  </si>
-  <si>
-    <t>RedDock</t>
-  </si>
-  <si>
-    <t>RedMarket</t>
-  </si>
-  <si>
-    <t>ThreatenWonder</t>
-  </si>
-  <si>
-    <t>DestroyWonder</t>
-  </si>
-  <si>
-    <t>BlueMonastery</t>
-  </si>
-  <si>
-    <t>Requires
-- Red Gold
-+ GreenGold</t>
-  </si>
-  <si>
-    <t>Requires
-- Purple Villagers</t>
-  </si>
-  <si>
-    <t>DefeatBurgundyAll</t>
-  </si>
-  <si>
-    <t>DefeatMetz</t>
-  </si>
-  <si>
-    <t>DefeatOrléans</t>
-  </si>
-  <si>
-    <t>DefeatRomanArmy</t>
-  </si>
-  <si>
-    <t>TributeBurgundyAll</t>
-  </si>
-  <si>
-    <t>CastleBurgundyAll</t>
-  </si>
-  <si>
-    <t>DefeatOrAllyBurgundyAny</t>
-  </si>
-  <si>
-    <t>Requires
--Town Center Wood/Stone</t>
-  </si>
-  <si>
-    <t>DefeatAlans</t>
-  </si>
-  <si>
-    <t>DefeatVisigoths</t>
-  </si>
-  <si>
-    <t>DefeatRomans</t>
-  </si>
-  <si>
-    <t>DefeatPatavium</t>
-  </si>
-  <si>
-    <t>DefeatMediolanum</t>
-  </si>
-  <si>
-    <t>DefeatAquileia</t>
-  </si>
-  <si>
-    <t>DefeatVerona</t>
-  </si>
-  <si>
-    <t>DefeatTheItalian</t>
-  </si>
-  <si>
-    <t>MeetThePope</t>
-  </si>
-  <si>
-    <t>DestroyPurpleWonder</t>
-  </si>
-  <si>
-    <t>DestroyGreenWonder</t>
-  </si>
-  <si>
-    <t>DestroyRedWonder</t>
-  </si>
-  <si>
-    <t>DestroyOrangeWonder</t>
-  </si>
-  <si>
-    <t>DestroyPurpleWonder2</t>
-  </si>
-  <si>
-    <t>Logic (Buildingsanity)</t>
   </si>
   <si>
     <t>Requires EITHER
@@ -4340,95 +4116,6 @@
 OR
 - Attilla's Base
 + Town Center Wood/Stone</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-- No Item
-OR
-- Town Center</t>
-  </si>
-  <si>
-    <t>Requires
--Dock</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-- Siege Workshop
-OR
-- Dock
-OR
--Castle
-+Mining Camp/Town Center</t>
-  </si>
-  <si>
-    <t>Requires
--Castle
-+Mining Camp/Town Center</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-- Siege Workshop
-OR
--Castle
-+Mining Camp/Town Center</t>
-  </si>
-  <si>
-    <t>Requires
-- Town Center
-+ Castle</t>
-  </si>
-  <si>
-    <t>Requires
-- Town Center Wood/Stone</t>
-  </si>
-  <si>
-    <t>Requires
-- Purple Villagers
-+ Town Center Wood/Stone</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-(
-- Siege Workshop
-OR
-- Castle
-+ Mining Camp/Town Center)
-OR
-(
-- Town Center
-+ Siege Workshop
-OR
-- Castle)</t>
-  </si>
-  <si>
-    <t>Standard:
-No items required
-Moderate:
-Requires EITHER
-(
-- Siege Workshop
-OR
-- Castle
-+ Mining Camp/Town Center)
-OR
-(
-- Town Center
-+ Siege Workshop
-OR
-- Castle)</t>
-  </si>
-  <si>
-    <t>Requires
-- Town Center
-+ Market</t>
-  </si>
-  <si>
-    <t>Requires
-- Town Center
-+ 1 Non-Siege Military Building
-+ Castle
-OR
-- Siege Workshop</t>
   </si>
   <si>
     <t>Standard:
@@ -4445,9 +4132,6 @@
 + 1 Non-Siege Military Building</t>
   </si>
   <si>
-    <t>Requires Bleda's Base</t>
-  </si>
-  <si>
     <t>Town Center</t>
   </si>
   <si>
@@ -4456,19 +4140,6 @@
 + Town Center Wood/Stone
 OR
 Scythian Troops</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-- Town Center
-+ 1 Non-Siege Military Building
-OR
-No items required</t>
-  </si>
-  <si>
-    <t>Requires EITHER
-- Red Gold
-OR
-- GreenGold</t>
   </si>
   <si>
     <t>Destructible Buildings</t>
@@ -5362,12 +5033,83 @@
       <t>(not on Standard)</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Dark - Castle Age</t>
+  </si>
+  <si>
+    <t>Unrestricted, BUT:
+Requires EITHER
+- Bleda's Base
+OR
+- Attilla's Base
++ Town Center Wood/Stone
+Huns cannot build houses</t>
+  </si>
+  <si>
+    <t>Unrestricted, BUT:
+Requires EITHER
+- Bleda's Base
+OR
+- Attilla's Base
++ Town Center Wood/Stone</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <t>Unrestricted, BUT:
+Requires
+Purple Villagers
++ Town Center Wood/Stone
+-Huns cannot build houses</t>
+  </si>
+  <si>
+    <t>Unrestricted, BUT:
+Requires
+Purple Villagers
++ Town Center Wood/Stone</t>
+  </si>
+  <si>
+    <t>No Market
+Huns cannot build Houses</t>
+  </si>
+  <si>
+    <t>No Trade Carts</t>
+  </si>
+  <si>
+    <t>No Caravan
+No Coinage</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Fast Fire Ships</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Huns Cannot build Houses</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5590,6 +5332,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5688,36 +5437,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -5765,11 +5484,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5807,13 +5550,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5840,7 +5577,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5855,7 +5592,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5864,37 +5601,67 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6498,13 +6265,13 @@
         <v>74</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>278</v>
+        <v>190</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>73</v>
@@ -6570,9 +6337,7 @@
   <dimension ref="B1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6582,562 +6347,442 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="168.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="K14" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>200</v>
-      </c>
       <c r="H15" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>222</v>
+        <v>92</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>205</v>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>223</v>
+        <v>92</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>201</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="18" t="s">
+        <v>113</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>224</v>
+        <v>92</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>202</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>225</v>
+        <v>92</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>203</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>227</v>
+        <v>92</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>139</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>204</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>228</v>
+        <v>92</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>140</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>206</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="21" t="s">
+        <v>118</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="K21" s="20" t="s">
-        <v>233</v>
+        <v>92</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>145</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>208</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="G22" s="19" t="s">
+        <v>120</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>246</v>
+        <v>119</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>158</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="8"/>
-      <c r="K23" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="225" x14ac:dyDescent="0.25">
-      <c r="G24" s="23" t="s">
-        <v>209</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="225" x14ac:dyDescent="0.25">
+      <c r="G24" s="21" t="s">
+        <v>121</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>229</v>
+        <v>123</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>141</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="G25" s="23" t="s">
-        <v>210</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="G25" s="21" t="s">
+        <v>122</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>230</v>
+        <v>119</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="K26" s="19" t="s">
-        <v>231</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K26" s="17" t="s">
+        <v>143</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="K27" s="19" t="s">
-        <v>232</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K27" s="17" t="s">
+        <v>144</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-    </row>
-    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-    </row>
-    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
     </row>
     <row r="35" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -7148,8 +6793,7 @@
   <dimension ref="B1:L25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -7158,463 +6802,381 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>186</v>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="H6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="H19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="G12" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="17" t="s">
-        <v>208</v>
-      </c>
       <c r="H20" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K20" s="27" t="s">
-        <v>225</v>
+        <v>155</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>137</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="25"/>
-      <c r="K21" s="27" t="s">
-        <v>231</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="23"/>
+      <c r="K21" s="25" t="s">
+        <v>143</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="25"/>
-      <c r="K22" s="27" t="s">
-        <v>218</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="23"/>
+      <c r="K22" s="25" t="s">
+        <v>130</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="25"/>
-      <c r="K23" s="17" t="s">
-        <v>232</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="23"/>
+      <c r="K23" s="15" t="s">
+        <v>144</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K24" s="17" t="s">
-        <v>245</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="K25" s="19" t="s">
-        <v>246</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K25" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>181</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7624,9 +7186,7 @@
   <dimension ref="B1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -7636,510 +7196,395 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K20" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K25" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K22" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K23" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K24" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K25" s="19" t="s">
-        <v>228</v>
-      </c>
       <c r="L25" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K26" s="19" t="s">
-        <v>259</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K26" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K27" s="19" t="s">
-        <v>260</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K27" s="17" t="s">
+        <v>172</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K28" s="19" t="s">
-        <v>261</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K28" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -8150,9 +7595,7 @@
   <dimension ref="B1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -8162,440 +7605,424 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H14" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="H21" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+    </row>
+    <row r="24" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+    </row>
+    <row r="25" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="N25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G11" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G12" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G13" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G14" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G15" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G16" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K22" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-    </row>
-    <row r="24" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="N25" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="26" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G26" s="21" t="s">
-        <v>275</v>
-      </c>
       <c r="H26" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
+        <v>174</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
     </row>
     <row r="27" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G27" s="21" t="s">
-        <v>276</v>
+      <c r="G27" s="19" t="s">
+        <v>188</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
+        <v>174</v>
+      </c>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8605,9 +8032,7 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -8617,515 +8042,517 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="132" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="132" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>290</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="20" t="s">
+      <c r="H21" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="20" t="s">
+      <c r="H24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G15" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G16" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="L21" s="32" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="26" t="s">
+      <c r="H30" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-    </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-    </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
+      <c r="H31" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9135,9 +8562,7 @@
   <dimension ref="B1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -9147,532 +8572,471 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="G3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="G6" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="G7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="G8" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="G9" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="G10" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="G11" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="G12" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="G13" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="G14" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="G15" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="H15" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="G16" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="21" t="s">
+      <c r="H24" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="318.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="300" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="318.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="K26" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G27" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K27" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G28" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K28" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="L28" s="36" t="s">
-        <v>112</v>
+      <c r="L28" s="34" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="H29" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
+      <c r="G29" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
+++ b/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26CAA05-136F-43AD-90F3-9ADBFE364E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0A3C0-2BAE-4011-AADE-0110504B436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="6" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="4" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Attila the Hun" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="238">
   <si>
     <t>Scenario</t>
   </si>
@@ -5089,10 +5089,6 @@
     <t>No Trade Carts</t>
   </si>
   <si>
-    <t>No Caravan
-No Coinage</t>
-  </si>
-  <si>
     <t>Castle - Imperial Age</t>
   </si>
   <si>
@@ -5103,13 +5099,92 @@
   </si>
   <si>
     <t>Huns Cannot build Houses</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unrestricted, BUT:
+Requires EITHER
+- Bleda's Base
+OR
+- Attilla's Base
++ Town Center Wood/Stone
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Loom and Murder Holes researched automatically</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No Caravan
+No Coinage
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes researched automatically</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Murder Holes researched automatically</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5338,6 +5413,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5634,6 +5715,18 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5650,18 +5743,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6347,11 +6428,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -6366,11 +6447,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -6407,7 +6488,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="13" t="s">
         <v>224</v>
       </c>
@@ -6415,7 +6496,7 @@
         <v>225</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>100</v>
@@ -6431,9 +6512,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="9" t="s">
         <v>101</v>
       </c>
@@ -6448,9 +6529,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="14" t="s">
         <v>102</v>
       </c>
@@ -6465,9 +6546,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="15" t="s">
         <v>103</v>
       </c>
@@ -6482,9 +6563,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="16" t="s">
         <v>104</v>
       </c>
@@ -6499,9 +6580,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="15" t="s">
         <v>109</v>
       </c>
@@ -6516,9 +6597,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="15" t="s">
         <v>105</v>
       </c>
@@ -6533,9 +6614,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="16" t="s">
         <v>106</v>
       </c>
@@ -6550,9 +6631,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="16" t="s">
         <v>107</v>
       </c>
@@ -6567,9 +6648,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="17" t="s">
         <v>111</v>
       </c>
@@ -6584,9 +6665,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="17" t="s">
         <v>112</v>
       </c>
@@ -6601,9 +6682,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="20" t="s">
         <v>117</v>
       </c>
@@ -6803,11 +6884,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -6822,11 +6903,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -6887,9 +6968,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="19" t="s">
         <v>112</v>
       </c>
@@ -6904,9 +6985,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="24" t="s">
         <v>103</v>
       </c>
@@ -6921,9 +7002,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="24" t="s">
         <v>216</v>
       </c>
@@ -6938,9 +7019,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="24" t="s">
         <v>151</v>
       </c>
@@ -6955,9 +7036,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="24" t="s">
         <v>146</v>
       </c>
@@ -6972,9 +7053,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="25" t="s">
         <v>147</v>
       </c>
@@ -6989,9 +7070,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
@@ -7006,9 +7087,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="28" t="s">
         <v>148</v>
       </c>
@@ -7023,9 +7104,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="28" t="s">
         <v>149</v>
       </c>
@@ -7040,9 +7121,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="9" t="s">
         <v>150</v>
       </c>
@@ -7057,9 +7138,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="9" t="s">
         <v>152</v>
       </c>
@@ -7196,11 +7277,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -7215,11 +7296,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -7256,15 +7337,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="47" t="s">
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="47" t="s">
-        <v>231</v>
+      <c r="D5" s="41" t="s">
+        <v>236</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>160</v>
@@ -7280,9 +7361,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="18" t="s">
         <v>112</v>
       </c>
@@ -7297,9 +7378,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="18" t="s">
         <v>161</v>
       </c>
@@ -7314,9 +7395,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="18" t="s">
         <v>111</v>
       </c>
@@ -7331,9 +7412,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
@@ -7348,9 +7429,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="19" t="s">
         <v>103</v>
       </c>
@@ -7365,9 +7446,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="19" t="s">
         <v>162</v>
       </c>
@@ -7382,9 +7463,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="19" t="s">
         <v>215</v>
       </c>
@@ -7399,9 +7480,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="21" t="s">
         <v>163</v>
       </c>
@@ -7416,9 +7497,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="17" t="s">
         <v>146</v>
       </c>
@@ -7433,9 +7514,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="17" t="s">
         <v>147</v>
       </c>
@@ -7450,9 +7531,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="18" t="s">
         <v>120</v>
       </c>
@@ -7605,11 +7686,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -7624,11 +7705,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="B3" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -7665,15 +7746,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" s="47" t="s">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="41" t="s">
         <v>234</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>237</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>101</v>
@@ -7689,9 +7770,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="9" t="s">
         <v>159</v>
       </c>
@@ -7706,9 +7787,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="15" t="s">
         <v>109</v>
       </c>
@@ -7723,9 +7804,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="15" t="s">
         <v>161</v>
       </c>
@@ -7740,9 +7821,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="15" t="s">
         <v>162</v>
       </c>
@@ -7757,9 +7838,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="15" t="s">
         <v>154</v>
       </c>
@@ -7774,9 +7855,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="24" t="s">
         <v>175</v>
       </c>
@@ -7791,9 +7872,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="24" t="s">
         <v>176</v>
       </c>
@@ -7808,9 +7889,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="24" t="s">
         <v>115</v>
       </c>
@@ -7825,9 +7906,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="24" t="s">
         <v>177</v>
       </c>
@@ -7842,9 +7923,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="24" t="s">
         <v>178</v>
       </c>
@@ -7859,9 +7940,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="24" t="s">
         <v>179</v>
       </c>
@@ -8042,11 +8123,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -8061,11 +8142,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="B3" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="9" t="s">
         <v>98</v>
       </c>
@@ -8103,14 +8184,14 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>233</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>101</v>
@@ -8126,9 +8207,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="13" t="s">
         <v>99</v>
       </c>
@@ -8143,9 +8224,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="35" t="s">
         <v>105</v>
       </c>
@@ -8160,9 +8241,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="25" t="s">
         <v>154</v>
       </c>
@@ -8177,9 +8258,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
@@ -8194,9 +8275,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="18" t="s">
         <v>112</v>
       </c>
@@ -8211,9 +8292,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="18" t="s">
         <v>175</v>
       </c>
@@ -8228,9 +8309,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="18" t="s">
         <v>161</v>
       </c>
@@ -8245,9 +8326,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="20" t="s">
         <v>193</v>
       </c>
@@ -8262,9 +8343,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="18" t="s">
         <v>181</v>
       </c>
@@ -8279,9 +8360,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="18" t="s">
         <v>194</v>
       </c>
@@ -8296,9 +8377,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="18" t="s">
         <v>218</v>
       </c>
@@ -8572,11 +8653,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -8591,11 +8672,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="B3" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>98</v>
       </c>
@@ -8633,14 +8714,14 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>233</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>159</v>
@@ -8656,9 +8737,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
       <c r="G6" s="14" t="s">
         <v>204</v>
       </c>
@@ -8673,9 +8754,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
       <c r="G7" s="19" t="s">
         <v>109</v>
       </c>
@@ -8690,9 +8771,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="43"/>
       <c r="G8" s="19" t="s">
         <v>115</v>
       </c>
@@ -8707,9 +8788,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="19" t="s">
         <v>161</v>
       </c>
@@ -8724,9 +8805,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
       <c r="G10" s="19" t="s">
         <v>200</v>
       </c>
@@ -8741,9 +8822,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
       <c r="G11" s="19" t="s">
         <v>147</v>
       </c>
@@ -8758,9 +8839,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
       <c r="G12" s="19" t="s">
         <v>176</v>
       </c>
@@ -8775,9 +8856,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
       <c r="G13" s="21" t="s">
         <v>205</v>
       </c>
@@ -8792,9 +8873,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="43"/>
       <c r="G14" s="19" t="s">
         <v>177</v>
       </c>
@@ -8809,9 +8890,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="G15" s="19" t="s">
         <v>178</v>
       </c>
@@ -8826,9 +8907,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
       <c r="G16" s="18" t="s">
         <v>188</v>
       </c>

--- a/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
+++ b/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0A3C0-2BAE-4011-AADE-0110504B436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC59E47E-1DFE-4CF1-BC5F-0464CFE37DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="4" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="6" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Attila the Hun" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="246">
   <si>
     <t>Scenario</t>
   </si>
@@ -5178,6 +5178,30 @@
       <t>:
 Murder Holes researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Mangudai</t>
+  </si>
+  <si>
+    <t>Castle (Only on Standard)</t>
+  </si>
+  <si>
+    <t>Mining Camp (Only on Standard)</t>
   </si>
 </sst>
 </file>
@@ -5429,7 +5453,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -5589,11 +5613,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5724,9 +5781,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5743,6 +5797,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6419,6 +6491,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6428,11 +6501,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -6447,11 +6520,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -6528,7 +6601,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -6545,10 +6618,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>103</v>
       </c>
@@ -6563,9 +6645,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>130</v>
+      </c>
       <c r="G9" s="16" t="s">
         <v>104</v>
       </c>
@@ -6580,9 +6669,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>94</v>
+      </c>
       <c r="G10" s="15" t="s">
         <v>109</v>
       </c>
@@ -6597,9 +6693,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>128</v>
+      </c>
       <c r="G11" s="15" t="s">
         <v>105</v>
       </c>
@@ -6614,9 +6715,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>129</v>
+      </c>
       <c r="G12" s="16" t="s">
         <v>106</v>
       </c>
@@ -6631,9 +6737,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="51" t="s">
+        <v>130</v>
+      </c>
       <c r="G13" s="16" t="s">
         <v>107</v>
       </c>
@@ -6648,9 +6757,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="51" t="s">
+        <v>131</v>
+      </c>
       <c r="G14" s="17" t="s">
         <v>111</v>
       </c>
@@ -6665,9 +6777,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="51" t="s">
+        <v>126</v>
+      </c>
       <c r="G15" s="17" t="s">
         <v>112</v>
       </c>
@@ -6682,9 +6797,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="51" t="s">
+        <v>127</v>
+      </c>
       <c r="G16" s="20" t="s">
         <v>117</v>
       </c>
@@ -6698,7 +6816,13 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="41" t="s">
+        <v>132</v>
+      </c>
       <c r="G17" s="18" t="s">
         <v>113</v>
       </c>
@@ -6712,7 +6836,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="20" t="s">
         <v>114</v>
       </c>
@@ -6726,7 +6854,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="19" t="s">
         <v>115</v>
       </c>
@@ -6740,7 +6872,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="G20" s="19" t="s">
         <v>116</v>
       </c>
@@ -6754,7 +6890,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="G21" s="21" t="s">
         <v>118</v>
       </c>
@@ -6768,7 +6908,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="G22" s="19" t="s">
         <v>120</v>
       </c>
@@ -6782,12 +6922,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="K23" s="17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="225" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="G24" s="21" t="s">
         <v>121</v>
       </c>
@@ -6801,7 +6941,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="G25" s="21" t="s">
         <v>122</v>
       </c>
@@ -6815,7 +6955,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="K26" s="17" t="s">
         <v>143</v>
       </c>
@@ -6823,7 +6963,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="K27" s="17" t="s">
         <v>144</v>
       </c>
@@ -6831,19 +6971,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
     </row>
@@ -6875,6 +7015,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6884,11 +7025,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -6903,11 +7044,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -6984,7 +7125,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -7001,10 +7142,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="24" t="s">
         <v>216</v>
       </c>
@@ -7019,9 +7169,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="52"/>
       <c r="G9" s="24" t="s">
         <v>151</v>
       </c>
@@ -7036,9 +7191,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="52"/>
       <c r="G10" s="24" t="s">
         <v>146</v>
       </c>
@@ -7053,9 +7213,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="52"/>
       <c r="G11" s="25" t="s">
         <v>147</v>
       </c>
@@ -7070,9 +7233,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="52"/>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
@@ -7087,9 +7253,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="E13" s="52"/>
       <c r="G13" s="28" t="s">
         <v>148</v>
       </c>
@@ -7104,9 +7273,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="52"/>
       <c r="G14" s="28" t="s">
         <v>149</v>
       </c>
@@ -7121,9 +7293,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="G15" s="9" t="s">
         <v>150</v>
       </c>
@@ -7138,9 +7311,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="G16" s="9" t="s">
         <v>152</v>
       </c>
@@ -7154,7 +7328,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="G17" s="9" t="s">
         <v>153</v>
       </c>
@@ -7168,7 +7346,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="17" t="s">
         <v>154</v>
       </c>
@@ -7182,7 +7364,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="22" t="s">
         <v>115</v>
       </c>
@@ -7196,7 +7382,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="G20" s="15" t="s">
         <v>120</v>
       </c>
@@ -7210,7 +7400,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="G21" s="23"/>
       <c r="K21" s="25" t="s">
         <v>143</v>
@@ -7219,7 +7413,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="23"/>
       <c r="K22" s="25" t="s">
         <v>130</v>
@@ -7228,7 +7422,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="23"/>
       <c r="K23" s="15" t="s">
         <v>144</v>
@@ -7237,7 +7431,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K24" s="15" t="s">
         <v>157</v>
       </c>
@@ -7245,7 +7439,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="K25" s="17" t="s">
         <v>158</v>
       </c>
@@ -7267,7 +7461,7 @@
   <dimension ref="B1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -7277,11 +7471,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -7296,11 +7490,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -7377,7 +7571,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -7394,10 +7588,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="18" t="s">
         <v>111</v>
       </c>
@@ -7412,9 +7615,13 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="52"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
@@ -7429,9 +7636,13 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="52"/>
       <c r="G10" s="19" t="s">
         <v>103</v>
       </c>
@@ -7446,9 +7657,13 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="52"/>
       <c r="G11" s="19" t="s">
         <v>162</v>
       </c>
@@ -7463,9 +7678,11 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="52"/>
       <c r="G12" s="19" t="s">
         <v>215</v>
       </c>
@@ -7480,9 +7697,11 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="52"/>
       <c r="G13" s="21" t="s">
         <v>163</v>
       </c>
@@ -7497,9 +7716,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="G14" s="17" t="s">
         <v>146</v>
       </c>
@@ -7514,9 +7734,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="G15" s="17" t="s">
         <v>147</v>
       </c>
@@ -7531,9 +7752,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="G16" s="18" t="s">
         <v>120</v>
       </c>
@@ -7547,7 +7769,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="G17" s="20" t="s">
         <v>164</v>
       </c>
@@ -7561,7 +7787,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="29" t="s">
         <v>165</v>
       </c>
@@ -7575,7 +7805,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="29" t="s">
         <v>166</v>
       </c>
@@ -7589,7 +7823,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="K20" s="17" t="s">
         <v>168</v>
       </c>
@@ -7597,7 +7835,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="K21" s="17" t="s">
         <v>169</v>
       </c>
@@ -7605,7 +7847,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K22" s="17" t="s">
         <v>170</v>
       </c>
@@ -7613,7 +7855,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K23" s="17" t="s">
         <v>143</v>
       </c>
@@ -7621,7 +7863,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K24" s="17" t="s">
         <v>142</v>
       </c>
@@ -7629,7 +7871,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K25" s="17" t="s">
         <v>140</v>
       </c>
@@ -7637,7 +7879,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K26" s="17" t="s">
         <v>171</v>
       </c>
@@ -7645,7 +7887,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K27" s="17" t="s">
         <v>172</v>
       </c>
@@ -7653,7 +7895,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K28" s="17" t="s">
         <v>173</v>
       </c>
@@ -7677,6 +7919,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -7686,11 +7929,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -7705,11 +7948,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
@@ -7786,7 +8029,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -7803,10 +8046,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>161</v>
       </c>
@@ -7821,9 +8073,12 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="G9" s="15" t="s">
         <v>162</v>
       </c>
@@ -7838,9 +8093,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="G10" s="15" t="s">
         <v>154</v>
       </c>
@@ -7855,9 +8113,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="G11" s="24" t="s">
         <v>175</v>
       </c>
@@ -7872,9 +8131,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="G12" s="24" t="s">
         <v>176</v>
       </c>
@@ -7889,9 +8149,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="G13" s="24" t="s">
         <v>115</v>
       </c>
@@ -7906,9 +8167,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="G14" s="24" t="s">
         <v>177</v>
       </c>
@@ -7923,9 +8185,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="G15" s="24" t="s">
         <v>178</v>
       </c>
@@ -7940,9 +8203,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="G16" s="24" t="s">
         <v>179</v>
       </c>
@@ -7956,7 +8220,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="G17" s="24" t="s">
         <v>180</v>
       </c>
@@ -7970,7 +8238,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="24" t="s">
         <v>147</v>
       </c>
@@ -7984,7 +8256,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="24" t="s">
         <v>181</v>
       </c>
@@ -7998,7 +8274,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="G20" s="24" t="s">
         <v>182</v>
       </c>
@@ -8012,7 +8292,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="G21" s="24" t="s">
         <v>186</v>
       </c>
@@ -8026,7 +8310,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="24" t="s">
         <v>183</v>
       </c>
@@ -8040,7 +8324,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="17" t="s">
         <v>184</v>
       </c>
@@ -8050,7 +8334,7 @@
       <c r="K23" s="31"/>
       <c r="L23" s="31"/>
     </row>
-    <row r="24" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="22" t="s">
         <v>185</v>
       </c>
@@ -8060,7 +8344,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="19" t="s">
         <v>161</v>
       </c>
@@ -8073,7 +8357,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="19" t="s">
         <v>187</v>
       </c>
@@ -8083,7 +8367,7 @@
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="19" t="s">
         <v>188</v>
       </c>
@@ -8093,7 +8377,7 @@
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="K28" s="23"/>
@@ -8114,6 +8398,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -8123,11 +8408,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -8142,11 +8427,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="9" t="s">
         <v>98</v>
       </c>
@@ -8223,7 +8508,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -8240,10 +8525,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="25" t="s">
         <v>154</v>
       </c>
@@ -8258,9 +8552,12 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="G9" s="18" t="s">
         <v>109</v>
       </c>
@@ -8275,9 +8572,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="G10" s="18" t="s">
         <v>112</v>
       </c>
@@ -8292,9 +8592,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="G11" s="18" t="s">
         <v>175</v>
       </c>
@@ -8309,9 +8612,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="G12" s="18" t="s">
         <v>161</v>
       </c>
@@ -8326,9 +8630,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="G13" s="20" t="s">
         <v>193</v>
       </c>
@@ -8343,9 +8648,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="G14" s="18" t="s">
         <v>181</v>
       </c>
@@ -8360,9 +8666,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="G15" s="18" t="s">
         <v>194</v>
       </c>
@@ -8377,9 +8684,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="G16" s="18" t="s">
         <v>218</v>
       </c>
@@ -8393,7 +8701,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="G17" s="18" t="s">
         <v>195</v>
       </c>
@@ -8407,7 +8719,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="18" t="s">
         <v>217</v>
       </c>
@@ -8421,7 +8737,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="18" t="s">
         <v>196</v>
       </c>
@@ -8435,7 +8755,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="G20" s="24" t="s">
         <v>115</v>
       </c>
@@ -8449,7 +8773,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="G21" s="24" t="s">
         <v>177</v>
       </c>
@@ -8463,7 +8791,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="33" t="s">
         <v>178</v>
       </c>
@@ -8473,7 +8801,7 @@
       <c r="K22" s="31"/>
       <c r="L22" s="31"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="24" t="s">
         <v>113</v>
       </c>
@@ -8483,7 +8811,7 @@
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
         <v>197</v>
       </c>
@@ -8493,7 +8821,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="18" t="s">
         <v>198</v>
       </c>
@@ -8503,7 +8831,7 @@
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="17" t="s">
         <v>111</v>
       </c>
@@ -8513,7 +8841,7 @@
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="29" t="s">
         <v>199</v>
       </c>
@@ -8523,7 +8851,7 @@
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="17" t="s">
         <v>185</v>
       </c>
@@ -8533,7 +8861,7 @@
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="17" t="s">
         <v>184</v>
       </c>
@@ -8543,7 +8871,7 @@
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="17" t="s">
         <v>200</v>
       </c>
@@ -8553,7 +8881,7 @@
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22" t="s">
         <v>201</v>
       </c>
@@ -8563,7 +8891,7 @@
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
       <c r="K32" s="23"/>
@@ -8644,6 +8972,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -8653,11 +8982,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
       <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
@@ -8672,11 +9001,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
       <c r="G3" s="6" t="s">
         <v>98</v>
       </c>
@@ -8753,7 +9082,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -8770,10 +9099,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="G8" s="19" t="s">
         <v>115</v>
       </c>
@@ -8788,9 +9126,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="52"/>
       <c r="G9" s="19" t="s">
         <v>161</v>
       </c>
@@ -8804,10 +9147,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="52"/>
       <c r="G10" s="19" t="s">
         <v>200</v>
       </c>
@@ -8821,10 +9169,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="52"/>
       <c r="G11" s="19" t="s">
         <v>147</v>
       </c>
@@ -8839,9 +9192,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="G12" s="19" t="s">
         <v>176</v>
       </c>
@@ -8856,9 +9212,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="G13" s="21" t="s">
         <v>205</v>
       </c>
@@ -8873,9 +9232,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="G14" s="19" t="s">
         <v>177</v>
       </c>
@@ -8890,9 +9250,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="G15" s="19" t="s">
         <v>178</v>
       </c>
@@ -8907,9 +9268,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="G16" s="18" t="s">
         <v>188</v>
       </c>
@@ -8923,7 +9285,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="G17" s="18" t="s">
         <v>146</v>
       </c>
@@ -8937,7 +9303,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="G18" s="18" t="s">
         <v>206</v>
       </c>
@@ -8951,7 +9321,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="G19" s="18" t="s">
         <v>181</v>
       </c>
@@ -8965,7 +9339,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="G20" s="26" t="s">
         <v>180</v>
       </c>
@@ -8979,7 +9357,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="G21" s="16" t="s">
         <v>207</v>
       </c>
@@ -8993,7 +9375,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="15" t="s">
         <v>201</v>
       </c>
@@ -9007,7 +9389,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="15" t="s">
         <v>116</v>
       </c>
@@ -9021,7 +9403,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="15" t="s">
         <v>187</v>
       </c>
@@ -9035,7 +9417,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="17" t="s">
         <v>185</v>
       </c>
@@ -9049,7 +9431,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="318.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="G26" s="29" t="s">
         <v>208</v>
       </c>
@@ -9063,7 +9445,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="19" t="s">
         <v>209</v>
       </c>
@@ -9077,7 +9459,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G28" s="21" t="s">
         <v>210</v>
       </c>
@@ -9091,7 +9473,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G29" s="38" t="s">
         <v>165</v>
       </c>
@@ -9101,13 +9483,13 @@
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="31"/>
       <c r="H30" s="31"/>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="K31" s="23"/>
